--- a/atacseq/latest/atacseq.xlsx
+++ b/atacseq/latest/atacseq.xlsx
@@ -48,6 +48,11 @@
   <commentList>
     <comment ref="A1" authorId="1">
       <text>
+        <t>A styled paragraph describing the assay</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="1">
+      <text>
         <t>(Required) The unique identifier from HuBMAP or SenNet for the sample (such as a
 block, section, or suspension) used to perform the assay. For instance, in an
 RNAseq assay, the parent sample would be the suspension, while in imaging
@@ -56,7 +61,7 @@
 Example: HBM386.ZGKG.235, HBM672.MKPK.442</t>
       </text>
     </comment>
-    <comment ref="B1" authorId="1">
+    <comment ref="C1" authorId="1">
       <text>
         <t>A locally assigned identifier provided by the data provider for the dataset. It
 is used to reference an external metadata record that may be maintained
@@ -64,7 +69,7 @@
 Example: Visium_9OLC_A4_S1</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="1">
+    <comment ref="D1" authorId="1">
       <text>
         <t>(Required) The DOI for the protocols.io page that details the assay or the
 procedures used for sample procurement and preparation. For example, in the case
@@ -74,24 +79,24 @@
 Example: https://dx.doi.org/10.17504/protocols.io.eq2lyno9qvx9/v1</t>
       </text>
     </comment>
-    <comment ref="D1" authorId="1">
+    <comment ref="E1" authorId="1">
       <text>
         <t>(Required) The specific type of dataset being produced. Example: RNAseq</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="1">
+    <comment ref="F1" authorId="1">
       <text>
         <t>(Required) The analyte class which is the target molecule that the assay is
 measuring. Example: DNA</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="1">
+    <comment ref="G1" authorId="1">
       <text>
         <t>(Required) Indicates whether a specific molecule or set of molecules is targeted
 for detection or measurement by the assay. Example: Yes</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="1">
+    <comment ref="H1" authorId="1">
       <text>
         <t>(Required) The company that manufactures or supplies the acquisition instrument.
 An acquisition instrument is a device equipped with signal detection hardware
@@ -101,7 +106,7 @@
 "In-House". Example: Illumina</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="I1" authorId="1">
       <text>
         <t>(Required) The specific model of the acquisition instrument, as manufacturers
 often offer various versions with differing features or sensitivities. These
@@ -110,7 +115,7 @@
 the model is unknown, enter "Unknown". Example: HiSeq 4000</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
+    <comment ref="J1" authorId="1">
       <text>
         <t>(Required) The length of time the sample was stored prior to processing it. For
 assays performed on tissue sections, this refers to how long the tissue section
@@ -119,32 +124,32 @@
 suspension was stored before library construction started. Example: 12</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="1">
+    <comment ref="K1" authorId="1">
       <text>
         <t>(Required) The unit of measurement used to specify the source storage duration
 value. Example: hour</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="1">
+    <comment ref="L1" authorId="1">
       <text>
         <t>The length of time since the acquisition instrument was last serviced or
 calibrated. This provides a metric for assessing drift in data capture. Example:
 10</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="1">
+    <comment ref="M1" authorId="1">
       <text>
         <t>The unit of measurement used to specify the time since acquisition instrument
 calibration value. Example: month</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="1">
+    <comment ref="N1" authorId="1">
       <text>
         <t>(Required) The name of the file containing the ORCID IDs for all contributors to
 this dataset. Example: ./contributors.csv</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="1">
+    <comment ref="O1" authorId="1">
       <text>
         <t>(Required) The top-level directory containing the raw and/or processed data. For
 a single dataset upload, this might be represented as ".", whereas for a data
@@ -156,7 +161,7 @@
 an internal metadata field used solely for data ingestion. Example: ./TEST001-RK</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="1">
+    <comment ref="P1" authorId="1">
       <text>
         <t>(Required) The position within a sequencing read where a barcode sequence
 begins. In sequencing libraries, barcodes—short DNA sequences used to tag
@@ -169,7 +174,7 @@
 Example: 0,38,76</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="1">
+    <comment ref="Q1" authorId="1">
       <text>
         <t>(Required) The sequencing read file contains the cell or capture spot barcode
 sequences. This information is essential when constructing sequencing libraries
@@ -178,13 +183,13 @@
 should be marked as "Not applicable". Example: Read 1 (R1)</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="1">
+    <comment ref="R1" authorId="1">
       <text>
         <t>(Required) The length of each cell or capture spot barcode in base pairs (bp).
 If the source material is not barcoded, enter "Not applicable". Example: 16</t>
       </text>
     </comment>
-    <comment ref="R1" authorId="1">
+    <comment ref="S1" authorId="1">
       <text>
         <t>(Required) The position within a sequencing read where the Unique Molecular
 Identifier (UMI) sequence begins. UMIs are short, random nucleotide sequences
@@ -192,34 +197,34 @@
 original molecule. If no UMI is used, enter "Not applicable". Example: 16</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="1">
+    <comment ref="T1" authorId="1">
       <text>
         <t>(Required) Specifies which sequencing read file contains the Unique Molecular
 Identifier (UMI) barcode. If no UMI is used, enter "Not applicable". Example:
 Read 1 (R1)</t>
       </text>
     </comment>
-    <comment ref="T1" authorId="1">
+    <comment ref="U1" authorId="1">
       <text>
         <t>(Required) The length of the Unique Molecular Identifier (UMI) in base pairs
 (bp). If no UMI is used, enter "Not applicable". Example: 8</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="1">
+    <comment ref="V1" authorId="1">
       <text>
         <t>(Required) The entity from which the analyte is captured. For example, in bulk
 sequencing, the source entity would be "tissue" while in single-cell sequencing,
 it would be "single cell". Example: single cell</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="1">
+    <comment ref="W1" authorId="1">
       <text>
         <t>The number of cells or nuclei that were input into the assay. This information
 is typically not available for assays performed on bulk tissue preparations, and
 therefore this field may be left blank. Example: 1000</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="1">
+    <comment ref="X1" authorId="1">
       <text>
         <t>(Required) The 5' and/or 3' adapter sequences used during library preparation to
 make the library compatible with the sequencing protocol and instrumentation.
@@ -228,57 +233,57 @@
 CTGTCTCTTATACACATCT</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="1">
+    <comment ref="Y1" authorId="1">
       <text>
         <t>(Required) The average size of sequencing library fragments, measured in base
 pairs (bp), as estimated by gel electrophoresis, BioAnalyzer, or TapeStation.
 Example: 200</t>
       </text>
     </comment>
-    <comment ref="Y1" authorId="1">
+    <comment ref="Z1" authorId="1">
       <text>
         <t>The amount of cDNA, after amplification, that was used for library construction.
 Example: 60</t>
       </text>
     </comment>
-    <comment ref="Z1" authorId="1">
+    <comment ref="AA1" authorId="1">
       <text>
         <t>The unit of measurement used to specify the library input amount value. Example:
 ng</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="1">
+    <comment ref="AB1" authorId="1">
       <text>
         <t>The total amount of library following the clean-up step after the final PCR
 amplification. To calculate, multiply the Qubit-measured concentration (ng/µl)
 by the elution volume (µl) obtained after the final clean-up. Example: 125</t>
       </text>
     </comment>
-    <comment ref="AB1" authorId="1">
+    <comment ref="AC1" authorId="1">
       <text>
         <t>The unit of measurement used to specify the library output amount value.
 Example: ng</t>
       </text>
     </comment>
-    <comment ref="AC1" authorId="1">
+    <comment ref="AD1" authorId="1">
       <text>
         <t>(Required) The concentration of the pooled library submitted for sequencing.
 Example: 2.5</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="1">
+    <comment ref="AE1" authorId="1">
       <text>
         <t>(Required) Unit of library concentration value.</t>
       </text>
     </comment>
-    <comment ref="AE1" authorId="1">
+    <comment ref="AF1" authorId="1">
       <text>
         <t>(Required) Indicates whether the sequencing library was prepared for single-end
 or paired-end sequencing. This information determines how reads are generated
 and aligned during data processing. Example: single-end</t>
       </text>
     </comment>
-    <comment ref="AF1" authorId="1">
+    <comment ref="AG1" authorId="1">
       <text>
         <t>(Required) The number of PCR cycles used specifically to add sequencing adapters
 and amplify the library during the indexing step. This count does not include
@@ -286,7 +291,7 @@
 "Number of iterations of cDNA amplification" field. Example: 8</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="1">
+    <comment ref="AH1" authorId="1">
       <text>
         <t>(Required) The reagent kit used to construct the sequencing library, including
 both the kit name and, if available, version and product number. If the library
@@ -294,7 +299,7 @@
 Chromium Next GEM Single Cell 5' Kit v2, 16 rxns; PN 1000263</t>
       </text>
     </comment>
-    <comment ref="AH1" authorId="1">
+    <comment ref="AI1" authorId="1">
       <text>
         <t>(Required) The reagent kit used to add index sequences to samples. Indexes
 enable multiplexing, allowing multiple libraries to be pooled and sequenced
@@ -306,27 +311,27 @@
 1000251</t>
       </text>
     </comment>
-    <comment ref="AI1" authorId="1">
+    <comment ref="AJ1" authorId="1">
       <text>
         <t>(Required) The specific sequencing barcode index set used, chosen from the
 sample indexing kit. For example, in the case of 10x, this might be "SI-GA-A1",
 whereas for Nextera, it could be "N505 - CTCCTTAC". Example: SI-GA-A1</t>
       </text>
     </comment>
-    <comment ref="AJ1" authorId="1">
+    <comment ref="AK1" authorId="1">
       <text>
         <t>(Required) Indicates whether the sequencing reaction was run in replicate. If
 "Yes," the corresponding FASTQ files in the dataset should be merged for
 analysis. Example: Yes</t>
       </text>
     </comment>
-    <comment ref="AK1" authorId="1">
+    <comment ref="AL1" authorId="1">
       <text>
         <t>The number of cells, nuclei, or capture spots expected to be captured by the
 assay. Example: 14336</t>
       </text>
     </comment>
-    <comment ref="AL1" authorId="1">
+    <comment ref="AM1" authorId="1">
       <text>
         <t>(Required) The reagent kit used to perform the sequencing run, including the
 platform, kit name, version, and product number when available. If the reagent
@@ -334,14 +339,14 @@
 NextSeq 500/550 Hi Output Kit 150 Cycles; v2.5; PN 20024907</t>
       </text>
     </comment>
-    <comment ref="AM1" authorId="1">
+    <comment ref="AN1" authorId="1">
       <text>
         <t>(Required) The number of sequencing cycles for each read and index in the
 sequencing run, typically reported as a comma-separated list in the order: Read
 1, i7 index, i5 index, and Read 2. Example: 50,8,16,50</t>
       </text>
     </comment>
-    <comment ref="AN1" authorId="1">
+    <comment ref="AO1" authorId="1">
       <text>
         <t>(Required) The reagent kit used for the transposition step, particularly if Tn5
 transposase was sourced from a commercial kit, including the platform, kit name,
@@ -351,13 +356,13 @@
 Gene Expression Reagent Bundle, 16 rxn; PN 1000283</t>
       </text>
     </comment>
-    <comment ref="AO1" authorId="1">
+    <comment ref="AP1" authorId="1">
       <text>
         <t>(Required) The method or approach used to capture accessible chromatin regions,
 typically reflecting the type of kit or protocol applied. Example: bulkATACseq</t>
       </text>
     </comment>
-    <comment ref="AP1" authorId="1">
+    <comment ref="AQ1" authorId="1">
       <text>
         <t>A lab-assigned identifier for the sequencing run, such as a chip ID, that
 enables users to determine which samples were processed together. To avoid ID
@@ -365,7 +370,7 @@
 of the sequencing center. Example: Broad_Chip1234</t>
       </text>
     </comment>
-    <comment ref="AQ1" authorId="1">
+    <comment ref="AR1" authorId="1">
       <text>
         <t>A lab-assigned identifier used to indicate which cells or nuclei were captured
 together in the same run. For example, in a 10X Genomics Chromium Controller
@@ -375,7 +380,7 @@
 the ID with the name of the sequencing center. Example: Broad_Batch1234</t>
       </text>
     </comment>
-    <comment ref="AR1" authorId="1">
+    <comment ref="AS1" authorId="1">
       <text>
         <t>The company that manufactures the instrument used to prepare the sample (e.g.,
 for staining or other processing steps) prior to the assay. If the instrument
@@ -383,7 +388,7 @@
 preparation occurred, enter "Not applicable". Example: 10X Genomics</t>
       </text>
     </comment>
-    <comment ref="AS1" authorId="1">
+    <comment ref="AT1" authorId="1">
       <text>
         <t>The specific model of the instrument used for sample preparation, such as
 staining. Manufacturers may offer multiple models with varying features or
@@ -392,7 +397,7 @@
 applicable". Example: Chromium X</t>
       </text>
     </comment>
-    <comment ref="AT1" authorId="1">
+    <comment ref="AU1" authorId="1">
       <text>
         <t>The reagent kit used in conjunction with the preparation instrument for sample
 processing (e.g., staining or labeling). If the reagent kit was prepared using a
@@ -400,7 +405,7 @@
 Single Cell Kit, 48 rxns; PN 1000120</t>
       </text>
     </comment>
-    <comment ref="AU1" authorId="1">
+    <comment ref="AV1" authorId="1">
       <text>
         <t>(Required) The unique string identifier for the metadata specification version,
 which is easily interpretable by computers for purposes of data validation and
@@ -412,7 +417,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="736">
+  <si>
+    <t>assay_description</t>
+  </si>
   <si>
     <t>parent_sample_id</t>
   </si>
@@ -516,6 +524,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000168</t>
   </si>
   <si>
+    <t>iCLAP</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000479</t>
+  </si>
+  <si>
     <t>seqFISH</t>
   </si>
   <si>
@@ -582,6 +596,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000207</t>
   </si>
   <si>
+    <t>MACSima</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000480</t>
+  </si>
+  <si>
     <t>CyTOF</t>
   </si>
   <si>
@@ -618,6 +638,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000219</t>
   </si>
   <si>
+    <t>DNA Methylation</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000490</t>
+  </si>
+  <si>
     <t>SIMS</t>
   </si>
   <si>
@@ -678,6 +704,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000209</t>
   </si>
   <si>
+    <t>Illumina Spatial ver0</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000487</t>
+  </si>
+  <si>
     <t>DART-FISH</t>
   </si>
   <si>
@@ -714,18 +746,36 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000301</t>
   </si>
   <si>
+    <t>Raman Imaging</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000475</t>
+  </si>
+  <si>
     <t>RNAseq (with probes)</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000311</t>
   </si>
   <si>
+    <t>Paired-Tag</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000492</t>
+  </si>
+  <si>
     <t>MS Lipidomics</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000405</t>
   </si>
   <si>
+    <t>STARmap</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000476</t>
+  </si>
+  <si>
     <t>MPLEx</t>
   </si>
   <si>
@@ -753,6 +803,12 @@
     <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C13201</t>
   </si>
   <si>
+    <t>Lipid + metabolite + protein</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000478</t>
+  </si>
+  <si>
     <t>RNA + protein</t>
   </si>
   <si>
@@ -939,6 +995,12 @@
     <t>https://identifiers.org/RRID:SCR_023605</t>
   </si>
   <si>
+    <t>Waters</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024589</t>
+  </si>
+  <si>
     <t>In-House</t>
   </si>
   <si>
@@ -993,12 +1055,24 @@
     <t>https://identifiers.org/RRID:SCR_023604</t>
   </si>
   <si>
+    <t>Miltenyi Biotec</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_008984</t>
+  </si>
+  <si>
     <t>Leica Biosystems</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_023603</t>
   </si>
   <si>
+    <t>Revvity</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027779</t>
+  </si>
+  <si>
     <t>Cytek Biosciences</t>
   </si>
   <si>
@@ -1080,6 +1154,12 @@
     <t>https://identifiers.org/RRID:SCR_024569</t>
   </si>
   <si>
+    <t>LSM 710 Confocal Microscope</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_018063</t>
+  </si>
+  <si>
     <t>NanoZoomer 2.0-HT</t>
   </si>
   <si>
@@ -1128,6 +1208,18 @@
     <t>https://identifiers.org/RRID:SCR_026452</t>
   </si>
   <si>
+    <t>DMi8</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_026672</t>
+  </si>
+  <si>
+    <t>Opera Phenix Plus HCS</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027780</t>
+  </si>
+  <si>
     <t>timsTOF Pro 2</t>
   </si>
   <si>
@@ -1170,6 +1262,12 @@
     <t>https://identifiers.org/RRID:SCR_027101</t>
   </si>
   <si>
+    <t>Orbitrap Fusion Tribrid</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_020559</t>
+  </si>
+  <si>
     <t>Custom: Multiphoton</t>
   </si>
   <si>
@@ -1296,6 +1394,18 @@
     <t>https://identifiers.org/RRID:SCR_027072</t>
   </si>
   <si>
+    <t>Opera Phenix HCS</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027817</t>
+  </si>
+  <si>
+    <t>Zeiss LightSheet Z.1</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_020919</t>
+  </si>
+  <si>
     <t>IN Cell Analyzer 2200</t>
   </si>
   <si>
@@ -1368,6 +1478,12 @@
     <t>https://identifiers.org/RRID:SCR_023692</t>
   </si>
   <si>
+    <t>NanoZoomer 2.0-RS</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_028001</t>
+  </si>
+  <si>
     <t>Axio Observer 3</t>
   </si>
   <si>
@@ -1413,6 +1529,12 @@
     <t>https://identifiers.org/RRID:SCR_016386</t>
   </si>
   <si>
+    <t>Q Exactive HF-X</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_020564</t>
+  </si>
+  <si>
     <t>solariX</t>
   </si>
   <si>
@@ -1437,6 +1559,18 @@
     <t>https://identifiers.org/RRID:SCR_023613</t>
   </si>
   <si>
+    <t>SYNAPT G2-Si</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027782</t>
+  </si>
+  <si>
+    <t>MACSima System</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_027923</t>
+  </si>
+  <si>
     <t>Biomark HD</t>
   </si>
   <si>
@@ -1737,6 +1871,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000366</t>
   </si>
   <si>
+    <t>10x Genomics; Chromium Next GEM Single Cell Fixed RNA Sample Preparation Kit, 16 rxns; PN 1000414</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000484</t>
+  </si>
+  <si>
     <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 4 slides, 16 reactions; PN 1000184</t>
   </si>
   <si>
@@ -2388,6 +2528,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000462</t>
   </si>
   <si>
+    <t>10x Genomics; Visium HD, Mouse Transcriptome, 6.5 mm, 4 runs; PN 1000676</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000494</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 48 rxns; PN 1000286</t>
   </si>
   <si>
@@ -2406,6 +2552,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000378</t>
   </si>
   <si>
+    <t>10x Genomics; Visium HD, Human Transcriptome, 6.5 mm, 4 runs; PN 1000675</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000493</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 16 rxns; PN 1000287</t>
   </si>
   <si>
@@ -2418,6 +2570,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000379</t>
   </si>
   <si>
+    <t>10x Genomics; Visium HD, Human Transcriptome, 11 mm, 4 runs; PN 1001037</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000495</t>
+  </si>
+  <si>
     <t>10x Genomics; Chromium GEM-X Single Cell 3' Kit v4, 16 rxns; PN 1000691</t>
   </si>
   <si>
@@ -2436,6 +2594,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000325</t>
   </si>
   <si>
+    <t>10x Genomics; Visium HD, Mouse Transcriptome, 11 mm, 4 runs; PN 1001038</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000496</t>
+  </si>
+  <si>
     <t>metadata_schema_id</t>
   </si>
   <si>
@@ -2454,7 +2618,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2025-11-20T09:40:16-08:00</t>
+    <t>2026-06-29T15:45:50-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -2513,11 +2677,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2575,56 +2740,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AV2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" style="2" width="14.39453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" style="3" width="5.46875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" style="4" width="20.234375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" style="5" width="10.59765625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" style="6" width="10.9296875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" style="7" width="9.40234375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" style="8" width="24.5546875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" style="9" width="24.0390625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" style="10" width="24.63671875" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" style="11" width="23.63671875" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" style="12" width="41.1015625" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" style="13" width="40.1015625" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" style="14" width="14.5859375" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" style="15" width="8.46484375" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" style="16" width="12.27734375" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" style="17" width="11.26171875" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" style="18" width="10.9140625" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" style="19" width="9.01953125" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" style="20" width="8.00390625" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" style="21" width="7.65625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" style="22" width="15.00390625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" style="23" width="25.9765625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" style="24" width="20.4609375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" style="25" width="24.20703125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" style="26" width="22.0703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" style="27" width="21.0703125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" style="28" width="23.17578125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" style="29" width="22.17578125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" style="30" width="21.9453125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" style="31" width="20.9453125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" style="32" width="11.296875" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" style="33" width="28.32421875" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" style="34" width="18.2734375" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" style="35" width="16.65234375" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" style="36" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" style="37" width="17.18359375" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" style="38" width="24.72265625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" style="39" width="19.05859375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" style="40" width="19.78125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" style="41" width="20.4296875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" style="42" width="17.71875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" style="43" width="16.94921875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" style="44" width="13.96484375" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" style="45" width="25.0859375" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" style="46" width="24.57421875" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" style="47" width="21.765625" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" style="48" width="16.91796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" style="2" width="14.46875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="2" max="2" style="3" width="14.39453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" style="4" width="5.46875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" style="5" width="20.234375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" style="6" width="10.59765625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" style="7" width="10.9296875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" style="8" width="9.40234375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" style="9" width="24.5546875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" style="10" width="24.0390625" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" style="11" width="24.63671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" style="12" width="23.63671875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" style="13" width="41.1015625" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" style="14" width="40.1015625" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" style="15" width="14.5859375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" style="16" width="8.46484375" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" style="17" width="12.27734375" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" style="18" width="11.26171875" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" style="19" width="10.9140625" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" style="20" width="9.01953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" style="21" width="8.00390625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" style="22" width="7.65625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" style="23" width="15.00390625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" style="24" width="25.9765625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" style="25" width="20.4609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" style="26" width="24.20703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" style="27" width="22.0703125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" style="28" width="21.0703125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" style="29" width="23.17578125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" style="30" width="22.17578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" style="31" width="21.9453125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" style="32" width="20.9453125" customWidth="true" bestFit="true"/>
+    <col min="32" max="32" style="33" width="11.296875" customWidth="true" bestFit="true"/>
+    <col min="33" max="33" style="34" width="28.32421875" customWidth="true" bestFit="true"/>
+    <col min="34" max="34" style="35" width="18.2734375" customWidth="true" bestFit="true"/>
+    <col min="35" max="35" style="36" width="16.65234375" customWidth="true" bestFit="true"/>
+    <col min="36" max="36" style="37" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" style="38" width="17.18359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" style="39" width="24.72265625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" style="40" width="19.05859375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" style="41" width="19.78125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" style="42" width="20.4296875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" style="43" width="17.71875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" style="44" width="16.94921875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" style="45" width="13.96484375" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" style="46" width="25.0859375" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" style="47" width="24.57421875" customWidth="true" bestFit="true"/>
+    <col min="47" max="47" style="48" width="21.765625" customWidth="true" bestFit="true"/>
+    <col min="48" max="48" style="49" width="16.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2641,261 +2807,264 @@
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>357</v>
+        <v>228</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>358</v>
+        <v>400</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>370</v>
+        <v>412</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>371</v>
+        <v>413</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>373</v>
+        <v>415</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>387</v>
+        <v>425</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>393</v>
+        <v>430</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>395</v>
+        <v>436</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>396</v>
+        <v>438</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>400</v>
+        <v>439</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>412</v>
+        <v>454</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>413</v>
+        <v>455</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>414</v>
+        <v>456</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>415</v>
+        <v>457</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>420</v>
+        <v>458</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>421</v>
+        <v>463</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>422</v>
+        <v>464</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>423</v>
+        <v>465</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>430</v>
+        <v>466</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>435</v>
+        <v>473</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>436</v>
+        <v>478</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>511</v>
+        <v>479</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>547</v>
+        <v>591</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>548</v>
+        <v>592</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>549</v>
+        <v>593</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>607</v>
+        <v>651</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>610</v>
+        <v>652</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>617</v>
+        <v>655</v>
       </c>
       <c r="AQ1" t="s" s="1">
-        <v>618</v>
+        <v>662</v>
       </c>
       <c r="AR1" t="s" s="1">
-        <v>619</v>
+        <v>663</v>
       </c>
       <c r="AS1" t="s" s="1">
-        <v>626</v>
+        <v>664</v>
       </c>
       <c r="AT1" t="s" s="1">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="AU1" t="s" s="1">
-        <v>674</v>
+        <v>698</v>
+      </c>
+      <c r="AV1" t="s" s="1">
+        <v>727</v>
       </c>
     </row>
     <row r="2">
-      <c r="D2" t="s" s="5">
-        <v>36</v>
-      </c>
-      <c r="AU2" t="s" s="48">
-        <v>675</v>
+      <c r="E2" t="s" s="6">
+        <v>39</v>
+      </c>
+      <c r="AV2" t="s" s="49">
+        <v>728</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="36">
-    <dataValidation type="list" sqref="D2:D1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'dataset_type'!$A$1:$A$51</formula1>
-    </dataValidation>
     <dataValidation type="list" sqref="E2:E1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'analyte_class'!$A$1:$A$17</formula1>
+      <formula1>'dataset_type'!$A$1:$A$58</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F2:F1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+      <formula1>'analyte_class'!$A$1:$A$18</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="G2:G1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'is_targeted'!$A$1:$A$2</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G2:G1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'acquisition_instrument_vendor'!$A$1:$A$30</formula1>
+    <dataValidation type="list" sqref="H2:H1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+      <formula1>'acquisition_instrument_vendor'!$A$1:$A$33</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H2:H1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'acquisition_instrument_model'!$A$1:$A$77</formula1>
+    <dataValidation type="list" sqref="I2:I1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+      <formula1>'acquisition_instrument_model'!$A$1:$A$87</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="I2:I1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="J2:J1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
       <formula1>0</formula1>
       <formula2/>
     </dataValidation>
-    <dataValidation type="list" sqref="J2:J1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="K2:K1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'source_storage_duration_unit'!$A$1:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="K2:K1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="L2:L1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
       <formula1>0</formula1>
       <formula2/>
     </dataValidation>
-    <dataValidation type="list" sqref="L2:L1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="M2:M1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'time_since_acquisition_instrume'!$A$1:$A$3</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="O2:O1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="P2:P1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'barcode_offset'!$A$1:$A$9</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="P2:P1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="Q2:Q1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'barcode_read'!$A$1:$A$3</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="Q2:Q1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="R2:R1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'barcode_size'!$A$1:$A$6</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="R2:R1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="S2:S1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'umi_offset'!$A$1:$A$4</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="S2:S1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="T2:T1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'umi_read'!$A$1:$A$3</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="T2:T1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="U2:U1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'umi_size'!$A$1:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="U2:U1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="V2:V1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'assay_input_entity'!$A$1:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" sqref="V2:V1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="whole" operator="between" sqref="W2:W1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" sqref="X2:X1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="whole" operator="between" sqref="Y2:Y1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" sqref="Y2:Y1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="decimal" operator="between" sqref="Z2:Z1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-3.4028235E38</formula1>
       <formula2>3.4028235E38</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="Z2:Z1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AA2:AA1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'library_input_amount_unit'!$A$1:$A$2</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" sqref="AA2:AA1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="decimal" operator="between" sqref="AB2:AB1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-3.4028235E38</formula1>
       <formula2>3.4028235E38</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="AB2:AB1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AC2:AC1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'library_output_amount_unit'!$A$1:$A$2</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" sqref="AC2:AC1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="decimal" operator="between" sqref="AD2:AD1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-3.4028235E38</formula1>
       <formula2>3.4028235E38</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="AD2:AD1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AE2:AE1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'library_concentration_unit'!$A$1:$A$3</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AE2:AE1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AF2:AF1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'library_layout'!$A$1:$A$2</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" sqref="AF2:AF1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="whole" operator="between" sqref="AG2:AG1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="AG2:AG1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'library_preparation_kit'!$A$1:$A$37</formula1>
+    <dataValidation type="list" sqref="AH2:AH1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+      <formula1>'library_preparation_kit'!$A$1:$A$38</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AH2:AH1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AI2:AI1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'sample_indexing_kit'!$A$1:$A$19</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AJ2:AJ1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AK2:AK1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'is_technical_replicate'!$A$1:$A$2</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" sqref="AK2:AK1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
+    <dataValidation type="whole" operator="between" sqref="AL2:AL1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="AL2:AL1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AM2:AM1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'sequencing_reagent_kit'!$A$1:$A$29</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AN2:AN1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AO2:AO1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'transposition_reagent_kit'!$A$1:$A$7</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AO2:AO1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AP2:AP1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'transposition_method'!$A$1:$A$4</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AR2:AR1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AS2:AS1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'preparation_instrument_vendor'!$A$1:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AS2:AS1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+    <dataValidation type="list" sqref="AT2:AT1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'preparation_instrument_model'!$A$1:$A$19</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AT2:AT1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'preparation_instrument_kit'!$A$1:$A$13</formula1>
+    <dataValidation type="list" sqref="AU2:AU1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
+      <formula1>'preparation_instrument_kit'!$A$1:$A$17</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2911,26 +3080,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>383</v>
+        <v>426</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>384</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>385</v>
+        <v>428</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>386</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -2945,32 +3114,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>388</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>389</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>390</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>391</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>392</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>214</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -2985,22 +3154,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>374</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>389</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>394</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>214</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3015,26 +3184,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>383</v>
+        <v>426</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>384</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>385</v>
+        <v>428</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>386</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -3049,27 +3218,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>375</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>397</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>398</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>399</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>214</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3084,42 +3253,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>401</v>
+        <v>444</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>402</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>403</v>
+        <v>446</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>404</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>405</v>
+        <v>448</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>406</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>407</v>
+        <v>450</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>408</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>409</v>
+        <v>452</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>410</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -3134,18 +3303,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>416</v>
+        <v>459</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>417</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>418</v>
+        <v>461</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>419</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -3160,18 +3329,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>416</v>
+        <v>459</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>417</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>418</v>
+        <v>461</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>419</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -3186,26 +3355,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>424</v>
+        <v>467</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>425</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>426</v>
+        <v>469</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>427</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>428</v>
+        <v>471</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>429</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -3220,18 +3389,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>431</v>
+        <v>474</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>432</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>433</v>
+        <v>476</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>434</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -3241,415 +3410,471 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -3659,303 +3884,311 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>437</v>
+        <v>480</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>438</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>439</v>
+        <v>482</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>440</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>441</v>
+        <v>484</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>442</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>443</v>
+        <v>486</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>444</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>445</v>
+        <v>488</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>446</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>447</v>
+        <v>490</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>448</v>
+        <v>491</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>449</v>
+        <v>492</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>450</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>451</v>
+        <v>494</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>452</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>453</v>
+        <v>496</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>454</v>
+        <v>497</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>455</v>
+        <v>498</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>456</v>
+        <v>499</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>457</v>
+        <v>500</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>458</v>
+        <v>501</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>459</v>
+        <v>502</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>460</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>461</v>
+        <v>504</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>462</v>
+        <v>505</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>464</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>465</v>
+        <v>508</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>466</v>
+        <v>509</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>467</v>
+        <v>510</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>468</v>
+        <v>511</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>469</v>
+        <v>512</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>470</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>471</v>
+        <v>514</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>472</v>
+        <v>515</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>473</v>
+        <v>516</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>474</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>475</v>
+        <v>518</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>476</v>
+        <v>519</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>477</v>
+        <v>520</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>478</v>
+        <v>521</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>479</v>
+        <v>522</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>480</v>
+        <v>523</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>482</v>
+        <v>525</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>483</v>
+        <v>526</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>484</v>
+        <v>527</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>485</v>
+        <v>528</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>486</v>
+        <v>529</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>487</v>
+        <v>530</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>488</v>
+        <v>531</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>489</v>
+        <v>532</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>490</v>
+        <v>533</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>491</v>
+        <v>534</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>492</v>
+        <v>535</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>493</v>
+        <v>536</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>494</v>
+        <v>537</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>495</v>
+        <v>538</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>496</v>
+        <v>539</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>497</v>
+        <v>540</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>498</v>
+        <v>541</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>499</v>
+        <v>542</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>500</v>
+        <v>543</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>501</v>
+        <v>544</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>502</v>
+        <v>545</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>503</v>
+        <v>546</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>504</v>
+        <v>547</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>505</v>
+        <v>548</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>506</v>
+        <v>549</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>507</v>
+        <v>550</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>508</v>
+        <v>551</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>509</v>
+        <v>552</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>510</v>
+        <v>553</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>554</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -3970,154 +4203,154 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>512</v>
+        <v>557</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>513</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>514</v>
+        <v>559</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>515</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>516</v>
+        <v>561</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>517</v>
+        <v>562</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>518</v>
+        <v>563</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>519</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>520</v>
+        <v>565</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>521</v>
+        <v>566</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>522</v>
+        <v>567</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>523</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>524</v>
+        <v>569</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>525</v>
+        <v>570</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>526</v>
+        <v>571</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>527</v>
+        <v>572</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>528</v>
+        <v>573</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>529</v>
+        <v>574</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>493</v>
+        <v>538</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>494</v>
+        <v>539</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>530</v>
+        <v>575</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>531</v>
+        <v>576</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>532</v>
+        <v>577</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>533</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>534</v>
+        <v>579</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>535</v>
+        <v>580</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>536</v>
+        <v>581</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>537</v>
+        <v>582</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>538</v>
+        <v>583</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>539</v>
+        <v>584</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>541</v>
+        <v>586</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>542</v>
+        <v>587</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>543</v>
+        <v>588</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>544</v>
+        <v>589</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>545</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -4132,12 +4365,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>142</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -4152,234 +4385,234 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>550</v>
+        <v>595</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>551</v>
+        <v>596</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>552</v>
+        <v>597</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>553</v>
+        <v>598</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>554</v>
+        <v>599</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>555</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>556</v>
+        <v>601</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>557</v>
+        <v>602</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>558</v>
+        <v>603</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>559</v>
+        <v>604</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>560</v>
+        <v>605</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>561</v>
+        <v>606</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>562</v>
+        <v>607</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>563</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>564</v>
+        <v>609</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>565</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>566</v>
+        <v>611</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>567</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>568</v>
+        <v>613</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>569</v>
+        <v>614</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>570</v>
+        <v>615</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>571</v>
+        <v>616</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>572</v>
+        <v>617</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>573</v>
+        <v>618</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>574</v>
+        <v>619</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>575</v>
+        <v>620</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>576</v>
+        <v>621</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>577</v>
+        <v>622</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>578</v>
+        <v>623</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>579</v>
+        <v>624</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>580</v>
+        <v>625</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>581</v>
+        <v>626</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>582</v>
+        <v>627</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>583</v>
+        <v>628</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>493</v>
+        <v>538</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>494</v>
+        <v>539</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>584</v>
+        <v>629</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>585</v>
+        <v>630</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>586</v>
+        <v>631</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>587</v>
+        <v>632</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>588</v>
+        <v>633</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>589</v>
+        <v>634</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>591</v>
+        <v>636</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>592</v>
+        <v>637</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>593</v>
+        <v>638</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>594</v>
+        <v>639</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>595</v>
+        <v>640</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>596</v>
+        <v>641</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>597</v>
+        <v>642</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>598</v>
+        <v>643</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>599</v>
+        <v>644</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>600</v>
+        <v>645</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>601</v>
+        <v>646</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>602</v>
+        <v>647</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>603</v>
+        <v>648</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>604</v>
+        <v>649</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>605</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -4394,58 +4627,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>503</v>
+        <v>548</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>504</v>
+        <v>549</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>489</v>
+        <v>534</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>490</v>
+        <v>535</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>451</v>
+        <v>496</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>452</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>493</v>
+        <v>538</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>494</v>
+        <v>539</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>477</v>
+        <v>522</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>478</v>
+        <v>523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>608</v>
+        <v>653</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>609</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -4460,34 +4693,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>611</v>
+        <v>656</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>612</v>
+        <v>657</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>613</v>
+        <v>658</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>614</v>
+        <v>659</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>615</v>
+        <v>660</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>616</v>
+        <v>661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>493</v>
+        <v>538</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>494</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -4502,90 +4735,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>176</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>194</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>620</v>
+        <v>665</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>621</v>
+        <v>666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>622</v>
+        <v>667</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>623</v>
+        <v>668</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>198</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>202</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>174</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>624</v>
+        <v>669</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>625</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
@@ -4600,154 +4833,154 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>287</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>627</v>
+        <v>672</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>628</v>
+        <v>673</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>219</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>629</v>
+        <v>674</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>630</v>
+        <v>675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>493</v>
+        <v>538</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>494</v>
+        <v>539</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>267</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>343</v>
+        <v>386</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>344</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>631</v>
+        <v>676</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>632</v>
+        <v>677</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>633</v>
+        <v>678</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>634</v>
+        <v>679</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>635</v>
+        <v>680</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>636</v>
+        <v>681</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>637</v>
+        <v>682</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>638</v>
+        <v>683</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>639</v>
+        <v>684</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>640</v>
+        <v>685</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>641</v>
+        <v>686</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>642</v>
+        <v>687</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>643</v>
+        <v>688</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>644</v>
+        <v>689</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>645</v>
+        <v>690</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>646</v>
+        <v>691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>647</v>
+        <v>692</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>648</v>
+        <v>693</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>649</v>
+        <v>694</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>650</v>
+        <v>695</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>652</v>
+        <v>697</v>
       </c>
     </row>
   </sheetData>
@@ -4757,111 +4990,143 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>654</v>
+        <v>699</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>655</v>
+        <v>700</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>656</v>
+        <v>701</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>657</v>
+        <v>702</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>489</v>
+        <v>534</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>490</v>
+        <v>535</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>658</v>
+        <v>703</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>659</v>
+        <v>704</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>660</v>
+        <v>705</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>661</v>
+        <v>706</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>662</v>
+        <v>707</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>663</v>
+        <v>708</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>493</v>
+        <v>709</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>494</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>664</v>
+        <v>538</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>665</v>
+        <v>539</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>666</v>
+        <v>711</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>667</v>
+        <v>712</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>503</v>
+        <v>713</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>504</v>
+        <v>714</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>668</v>
+        <v>715</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>669</v>
+        <v>716</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>670</v>
+        <v>548</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>671</v>
+        <v>549</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>672</v>
+        <v>717</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>673</v>
+        <v>718</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>719</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>723</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>725</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>726</v>
       </c>
     </row>
   </sheetData>
@@ -4882,30 +5147,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>676</v>
+        <v>729</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>677</v>
+        <v>730</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>679</v>
+        <v>732</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>681</v>
+        <v>734</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>678</v>
+        <v>731</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>680</v>
+        <v>733</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>682</v>
+        <v>735</v>
       </c>
     </row>
   </sheetData>
@@ -4915,143 +5180,151 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>116</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>118</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>122</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>128</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>130</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>132</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>134</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>138</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>140</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -5066,12 +5339,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>142</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -5081,247 +5354,271 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>146</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>148</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>152</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>156</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>158</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>168</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>172</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>174</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>176</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>178</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>180</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>182</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>186</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>188</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>196</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>202</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>204</v>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -5331,623 +5628,703 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:B87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>207</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>209</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>211</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>213</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>217</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>219</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>221</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>223</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>225</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>227</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>229</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>231</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>233</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>235</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>237</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>239</v>
+        <v>262</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>241</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>243</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>245</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>247</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>249</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>251</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>253</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>255</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>257</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>259</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>261</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>263</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>265</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>267</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>269</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>271</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>273</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>275</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>277</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>279</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>281</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>283</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>285</v>
+        <v>308</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>287</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>289</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>291</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>293</v>
+        <v>316</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>295</v>
+        <v>318</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>297</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>299</v>
+        <v>322</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>301</v>
+        <v>324</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>303</v>
+        <v>326</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>305</v>
+        <v>328</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>307</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>309</v>
+        <v>332</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>311</v>
+        <v>334</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>313</v>
+        <v>336</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>315</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>317</v>
+        <v>340</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>319</v>
+        <v>342</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>321</v>
+        <v>344</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>323</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>70</v>
+        <v>347</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>324</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>326</v>
+        <v>350</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>328</v>
+        <v>352</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>330</v>
+        <v>354</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>175</v>
+        <v>355</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>176</v>
+        <v>356</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>332</v>
+        <v>358</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>334</v>
+        <v>360</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>335</v>
+        <v>77</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>336</v>
+        <v>361</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>338</v>
+        <v>363</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>340</v>
+        <v>365</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>342</v>
+        <v>367</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>343</v>
+        <v>194</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>344</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>346</v>
+        <v>369</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>348</v>
+        <v>371</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>350</v>
+        <v>373</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>352</v>
+        <v>375</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>354</v>
+        <v>377</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>356</v>
+        <v>379</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>380</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>382</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>384</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>386</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>388</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>392</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>394</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>396</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>398</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -5962,42 +6339,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>359</v>
+        <v>402</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>360</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>361</v>
+        <v>404</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>362</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>363</v>
+        <v>406</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>364</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>365</v>
+        <v>408</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>366</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>367</v>
+        <v>410</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>368</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -6012,26 +6389,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>361</v>
+        <v>404</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>362</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>363</v>
+        <v>406</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>364</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>365</v>
+        <v>408</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>366</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -6046,47 +6423,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>374</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>375</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>376</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>377</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>378</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>379</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>380</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>381</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>214</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/atacseq/latest/atacseq.xlsx
+++ b/atacseq/latest/atacseq.xlsx
@@ -417,7 +417,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="745">
   <si>
     <t>assay_description</t>
   </si>
@@ -1148,6 +1148,12 @@
     <t>https://identifiers.org/RRID:SCR_025070</t>
   </si>
   <si>
+    <t>Orbitrap Astral</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_028684</t>
+  </si>
+  <si>
     <t>NovaSeq X</t>
   </si>
   <si>
@@ -1691,7 +1697,7 @@
     <t>10,48,86</t>
   </si>
   <si>
-    <t>0,20-23,41-44</t>
+    <t>0,20-23,51-54</t>
   </si>
   <si>
     <t>barcode_read</t>
@@ -1727,6 +1733,9 @@
     <t>8,6</t>
   </si>
   <si>
+    <t>14-17,14,14</t>
+  </si>
+  <si>
     <t>umi_offset</t>
   </si>
   <si>
@@ -2069,12 +2078,24 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000250</t>
   </si>
   <si>
+    <t>Epigenome Technologies; Multiplex Droplet Paired-Tag 16 Reaction Kit; PN MDP16101</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000499</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 4 rxns; PN 1000269</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000338</t>
   </si>
   <si>
+    <t>10x Genomics; GEM-X Flex GEM &amp; Library Kit, 4 rxns; PN 1000782</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000497</t>
+  </si>
+  <si>
     <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 8 rxns; PN 1000374</t>
   </si>
   <si>
@@ -2594,6 +2615,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000325</t>
   </si>
   <si>
+    <t>10x Genomics; GEM-X Flex Gene Expression Chip Kit, 4 chips; PN 1000791</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000498</t>
+  </si>
+  <si>
     <t>10x Genomics; Visium HD, Mouse Transcriptome, 11 mm, 4 runs; PN 1001038</t>
   </si>
   <si>
@@ -2618,7 +2645,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2026-06-29T15:45:50-07:00</t>
+    <t>2026-07-27T11:41:09-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -2822,121 +2849,121 @@
         <v>228</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="AQ1" t="s" s="1">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="AR1" t="s" s="1">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="AS1" t="s" s="1">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="AT1" t="s" s="1">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="AU1" t="s" s="1">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="AV1" t="s" s="1">
-        <v>727</v>
+        <v>736</v>
       </c>
     </row>
     <row r="2">
@@ -2944,7 +2971,7 @@
         <v>39</v>
       </c>
       <c r="AV2" t="s" s="49">
-        <v>728</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>
@@ -2962,7 +2989,7 @@
       <formula1>'acquisition_instrument_vendor'!$A$1:$A$33</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I2:I1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'acquisition_instrument_model'!$A$1:$A$87</formula1>
+      <formula1>'acquisition_instrument_model'!$A$1:$A$88</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="J2:J1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
       <formula1>0</formula1>
@@ -2985,7 +3012,7 @@
       <formula1>'barcode_read'!$A$1:$A$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="R2:R1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'barcode_size'!$A$1:$A$6</formula1>
+      <formula1>'barcode_size'!$A$1:$A$7</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="S2:S1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'umi_offset'!$A$1:$A$4</formula1>
@@ -3036,7 +3063,7 @@
       <formula2>2147483647</formula2>
     </dataValidation>
     <dataValidation type="list" sqref="AH2:AH1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'library_preparation_kit'!$A$1:$A$38</formula1>
+      <formula1>'library_preparation_kit'!$A$1:$A$40</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AI2:AI1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'sample_indexing_kit'!$A$1:$A$19</formula1>
@@ -3064,7 +3091,7 @@
       <formula1>'preparation_instrument_model'!$A$1:$A$19</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AU2:AU1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'preparation_instrument_kit'!$A$1:$A$17</formula1>
+      <formula1>'preparation_instrument_kit'!$A$1:$A$18</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -3080,10 +3107,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2">
@@ -3096,10 +3123,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -3109,36 +3136,41 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
         <v>237</v>
       </c>
     </row>
@@ -3154,17 +3186,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4">
@@ -3184,10 +3216,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2">
@@ -3200,10 +3232,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -3218,22 +3250,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5">
@@ -3253,42 +3285,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -3303,18 +3335,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -3329,18 +3361,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -3355,26 +3387,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -3389,18 +3421,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -3884,311 +3916,327 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>555</v>
+        <v>558</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>559</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>561</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -4203,18 +4251,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>558</v>
+        <v>565</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>560</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3">
@@ -4227,130 +4275,130 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>562</v>
+        <v>569</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>564</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>566</v>
+        <v>573</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>568</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>570</v>
+        <v>577</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>572</v>
+        <v>579</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>574</v>
+        <v>581</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>576</v>
+        <v>583</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>580</v>
+        <v>587</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>582</v>
+        <v>589</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>584</v>
+        <v>591</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>588</v>
+        <v>595</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>590</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -4385,234 +4433,234 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>596</v>
+        <v>603</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>600</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>602</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>604</v>
+        <v>611</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>606</v>
+        <v>613</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>608</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>610</v>
+        <v>617</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>612</v>
+        <v>619</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>614</v>
+        <v>621</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>616</v>
+        <v>623</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>618</v>
+        <v>625</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>620</v>
+        <v>627</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>624</v>
+        <v>631</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>626</v>
+        <v>633</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>628</v>
+        <v>635</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>630</v>
+        <v>637</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>632</v>
+        <v>639</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>634</v>
+        <v>641</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>636</v>
+        <v>643</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>638</v>
+        <v>645</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>640</v>
+        <v>647</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>642</v>
+        <v>649</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>644</v>
+        <v>651</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>646</v>
+        <v>653</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>648</v>
+        <v>655</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>650</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
@@ -4627,10 +4675,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2">
@@ -4643,42 +4691,42 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>654</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -4693,34 +4741,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>657</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>659</v>
+        <v>666</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>661</v>
+        <v>668</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
   </sheetData>
@@ -4767,18 +4815,18 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>666</v>
+        <v>673</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>668</v>
+        <v>675</v>
       </c>
     </row>
     <row r="7">
@@ -4815,10 +4863,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>670</v>
+        <v>677</v>
       </c>
     </row>
   </sheetData>
@@ -4833,10 +4881,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2">
@@ -4849,10 +4897,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>673</v>
+        <v>680</v>
       </c>
     </row>
     <row r="4">
@@ -4865,122 +4913,122 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>675</v>
+        <v>682</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>677</v>
+        <v>684</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>679</v>
+        <v>686</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>681</v>
+        <v>688</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>683</v>
+        <v>690</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>685</v>
+        <v>692</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>687</v>
+        <v>694</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>689</v>
+        <v>696</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>691</v>
+        <v>698</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>693</v>
+        <v>700</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>697</v>
+        <v>704</v>
       </c>
     </row>
   </sheetData>
@@ -4990,143 +5038,151 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>700</v>
+        <v>707</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>702</v>
+        <v>709</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>704</v>
+        <v>711</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>708</v>
+        <v>715</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>710</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>712</v>
+        <v>719</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>714</v>
+        <v>721</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>716</v>
+        <v>723</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>718</v>
+        <v>725</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>720</v>
+        <v>727</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>722</v>
+        <v>729</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>724</v>
+        <v>731</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>726</v>
+        <v>733</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>734</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>735</v>
       </c>
     </row>
   </sheetData>
@@ -5147,16 +5203,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>729</v>
+        <v>738</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>734</v>
+        <v>743</v>
       </c>
     </row>
     <row r="2">
@@ -5164,13 +5220,13 @@
         <v>39</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
   </sheetData>
@@ -5628,7 +5684,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6161,15 +6217,15 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>362</v>
+        <v>77</v>
       </c>
       <c r="B68" t="s" s="0">
         <v>363</v>
@@ -6193,18 +6249,18 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>194</v>
+        <v>368</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>195</v>
+        <v>369</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>368</v>
+        <v>194</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>369</v>
+        <v>195</v>
       </c>
     </row>
     <row r="73">
@@ -6325,6 +6381,14 @@
       </c>
       <c r="B87" t="s" s="0">
         <v>399</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>400</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -6339,42 +6403,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -6389,26 +6453,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -6423,42 +6487,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">

--- a/atacseq/latest/atacseq.xlsx
+++ b/atacseq/latest/atacseq.xlsx
@@ -63,10 +63,10 @@
     </comment>
     <comment ref="C1" authorId="1">
       <text>
-        <t>A locally assigned identifier provided by the data provider for the dataset. It
-is used to reference an external metadata record that may be maintained
-independently, enabling traceability and supporting provenance tracking.
-Example: Visium_9OLC_A4_S1</t>
+        <t>An identifier assigned by the data provider to reference an external metadata
+record for the dataset. The external record may be maintained independently and
+can support dataset traceability and provenance tracking. Leave this field empty
+if no such identifier exists.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="1">
@@ -417,7 +417,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="756">
   <si>
     <t>assay_description</t>
   </si>
@@ -1400,6 +1400,12 @@
     <t>https://identifiers.org/RRID:SCR_027072</t>
   </si>
   <si>
+    <t>iScan System</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_016388</t>
+  </si>
+  <si>
     <t>Opera Phenix HCS</t>
   </si>
   <si>
@@ -1679,12 +1685,18 @@
     <t>0</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
+    <t>0,14</t>
+  </si>
+  <si>
     <t>1,27</t>
   </si>
   <si>
@@ -1727,12 +1739,15 @@
     <t>40</t>
   </si>
   <si>
+    <t>8,6</t>
+  </si>
+  <si>
+    <t>10,10</t>
+  </si>
+  <si>
     <t>8,8,8</t>
   </si>
   <si>
-    <t>8,6</t>
-  </si>
-  <si>
     <t>14-17,14,14</t>
   </si>
   <si>
@@ -2231,6 +2246,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000463</t>
   </si>
   <si>
+    <t>Illumina; NextSeq 1000/2000 P2 XLEAP-SBS Reagent Kit (100 Cycles); PN 20100987</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000503</t>
+  </si>
+  <si>
     <t>Illumina; NovaSeq X Series 1.5B Reagent Kit (300 Cycle); PN 20104705</t>
   </si>
   <si>
@@ -2585,6 +2606,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000368</t>
   </si>
   <si>
+    <t>10x Genomics; Chromium Next GEM Chip J Single Cell Kit, 16 rxns; PN 1000230</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000263</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 16 rxns; PN 1000127</t>
   </si>
   <si>
@@ -2615,6 +2642,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000325</t>
   </si>
   <si>
+    <t>10x Genomics; Chromium Next GEM Chip J Single Cell Kit, 48 rxns; PN 1000234</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000262</t>
+  </si>
+  <si>
     <t>10x Genomics; GEM-X Flex Gene Expression Chip Kit, 4 chips; PN 1000791</t>
   </si>
   <si>
@@ -2645,7 +2678,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2026-07-27T11:41:09-07:00</t>
+    <t>2026-08-17T08:16:44-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -2849,121 +2882,121 @@
         <v>228</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="AQ1" t="s" s="1">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="AR1" t="s" s="1">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="AS1" t="s" s="1">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="AT1" t="s" s="1">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="AU1" t="s" s="1">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="AV1" t="s" s="1">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="2">
@@ -2971,7 +3004,7 @@
         <v>39</v>
       </c>
       <c r="AV2" t="s" s="49">
-        <v>737</v>
+        <v>748</v>
       </c>
     </row>
   </sheetData>
@@ -2989,7 +3022,7 @@
       <formula1>'acquisition_instrument_vendor'!$A$1:$A$33</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I2:I1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'acquisition_instrument_model'!$A$1:$A$88</formula1>
+      <formula1>'acquisition_instrument_model'!$A$1:$A$89</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="J2:J1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be greater than 0" showErrorMessage="true">
       <formula1>0</formula1>
@@ -3006,13 +3039,13 @@
       <formula1>'time_since_acquisition_instrume'!$A$1:$A$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="P2:P1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'barcode_offset'!$A$1:$A$9</formula1>
+      <formula1>'barcode_offset'!$A$1:$A$11</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="Q2:Q1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'barcode_read'!$A$1:$A$3</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="R2:R1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'barcode_size'!$A$1:$A$7</formula1>
+      <formula1>'barcode_size'!$A$1:$A$8</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="S2:S1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'umi_offset'!$A$1:$A$4</formula1>
@@ -3076,7 +3109,7 @@
       <formula2>2147483647</formula2>
     </dataValidation>
     <dataValidation type="list" sqref="AM2:AM1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'sequencing_reagent_kit'!$A$1:$A$29</formula1>
+      <formula1>'sequencing_reagent_kit'!$A$1:$A$30</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AO2:AO1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'transposition_reagent_kit'!$A$1:$A$7</formula1>
@@ -3091,7 +3124,7 @@
       <formula1>'preparation_instrument_model'!$A$1:$A$19</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AU2:AU1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'preparation_instrument_kit'!$A$1:$A$18</formula1>
+      <formula1>'preparation_instrument_kit'!$A$1:$A$20</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -3107,10 +3140,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2">
@@ -3123,10 +3156,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -3136,41 +3169,46 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
         <v>237</v>
       </c>
     </row>
@@ -3186,17 +3224,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4">
@@ -3216,10 +3254,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2">
@@ -3232,10 +3270,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -3250,22 +3288,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5">
@@ -3285,42 +3323,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -3335,18 +3373,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -3361,18 +3399,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -3387,26 +3425,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -3421,18 +3459,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -3921,322 +3959,322 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>546</v>
+        <v>551</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>554</v>
+        <v>559</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>558</v>
+        <v>563</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>562</v>
+        <v>567</v>
       </c>
     </row>
   </sheetData>
@@ -4251,18 +4289,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>565</v>
+        <v>570</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>567</v>
+        <v>572</v>
       </c>
     </row>
     <row r="3">
@@ -4275,130 +4313,130 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>575</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>577</v>
+        <v>582</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>583</v>
+        <v>588</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>587</v>
+        <v>592</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>597</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -4428,239 +4466,247 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>603</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>613</v>
+        <v>618</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>617</v>
+        <v>622</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>621</v>
+        <v>626</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>623</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>627</v>
+        <v>632</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>631</v>
+        <v>636</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>633</v>
+        <v>638</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>541</v>
+        <v>641</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>542</v>
+        <v>642</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>636</v>
+        <v>546</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>637</v>
+        <v>547</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>639</v>
+        <v>644</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>641</v>
+        <v>646</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>647</v>
+        <v>652</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>651</v>
+        <v>656</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>653</v>
+        <v>658</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>657</v>
+        <v>662</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>663</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>664</v>
       </c>
     </row>
   </sheetData>
@@ -4675,10 +4721,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="2">
@@ -4691,42 +4737,42 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>661</v>
+        <v>668</v>
       </c>
     </row>
   </sheetData>
@@ -4741,34 +4787,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>664</v>
+        <v>671</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>666</v>
+        <v>673</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>668</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -4815,18 +4861,18 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>673</v>
+        <v>680</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>675</v>
+        <v>682</v>
       </c>
     </row>
     <row r="7">
@@ -4863,10 +4909,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>677</v>
+        <v>684</v>
       </c>
     </row>
   </sheetData>
@@ -4897,10 +4943,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>680</v>
+        <v>687</v>
       </c>
     </row>
     <row r="4">
@@ -4913,18 +4959,18 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>682</v>
+        <v>689</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7">
@@ -4937,98 +4983,98 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>684</v>
+        <v>691</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>686</v>
+        <v>693</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>688</v>
+        <v>695</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>690</v>
+        <v>697</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>692</v>
+        <v>699</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>694</v>
+        <v>701</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>696</v>
+        <v>703</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>698</v>
+        <v>705</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>700</v>
+        <v>707</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>702</v>
+        <v>709</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>704</v>
+        <v>711</v>
       </c>
     </row>
   </sheetData>
@@ -5038,151 +5084,167 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>709</v>
+        <v>716</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>711</v>
+        <v>718</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>713</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>715</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>717</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>719</v>
+        <v>726</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>721</v>
+        <v>728</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>551</v>
+        <v>731</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>552</v>
+        <v>732</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>724</v>
+        <v>556</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>725</v>
+        <v>557</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>727</v>
+        <v>734</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>729</v>
+        <v>736</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>731</v>
+        <v>738</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>733</v>
+        <v>740</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>735</v>
+        <v>742</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>743</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>745</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>746</v>
       </c>
     </row>
   </sheetData>
@@ -5203,16 +5265,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>738</v>
+        <v>749</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>739</v>
+        <v>750</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>741</v>
+        <v>752</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>743</v>
+        <v>754</v>
       </c>
     </row>
     <row r="2">
@@ -5220,13 +5282,13 @@
         <v>39</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>744</v>
+        <v>755</v>
       </c>
     </row>
   </sheetData>
@@ -5684,7 +5746,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B88"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6225,15 +6287,15 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="B69" t="s" s="0">
         <v>365</v>
@@ -6257,18 +6319,18 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>194</v>
+        <v>370</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>195</v>
+        <v>371</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>370</v>
+        <v>194</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>371</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74">
@@ -6389,6 +6451,14 @@
       </c>
       <c r="B88" t="s" s="0">
         <v>401</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>402</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -6403,42 +6473,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -6453,26 +6523,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -6482,51 +6552,61 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
         <v>237</v>
       </c>
     </row>
